--- a/sources/metaPee/combined/subexposure_views/yes/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_combined.xlsx
+++ b/sources/metaPee/combined/subexposure_views/yes/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_combined.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -790,44 +790,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>pyridoxal_5_phosphate_plp</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.76</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.55</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0.1878635927204014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>10463250</v>
+        <v>910</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>15506</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pyridoxal_5_phosphate_plp</t>
+          <t>vitamin_b6</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -858,20 +852,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vitamin_b6</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
@@ -880,41 +874,47 @@
       </c>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>910</v>
+        <v>2296</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>455</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1.63</v>
+      </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
+        <v>89.2</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.3317714304045377</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>2296</v>
+        <v>10482060</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1142</v>
+        <v>15845</v>
       </c>
     </row>
     <row r="15">
@@ -1143,20 +1143,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vitamin_b1</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>2296</v>
+        <v>15914</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1142</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>vitamin_b1</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.92</v>
+        <v>2.53</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1196,29 +1196,29 @@
       </c>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>63257</v>
+        <v>2296</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>229</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.53</v>
+        <v>2.92</v>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1227,45 +1227,107 @@
       </c>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>2296</v>
+        <v>63257</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1142</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.84</v>
+        <v>2.53</v>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
+        <v>2296</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>carnitine</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>95958</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K27" s="2" t="n">
         <v>353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:K27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
